--- a/NECP Scenario/Results/Regional Results/EL62_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL62_Capacity.xlsx
@@ -507,25 +507,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.176538896974762E-11</v>
+        <v>1.737115686894722E-11</v>
       </c>
       <c r="C2">
-        <v>6.160906805952772E-12</v>
+        <v>9.096361742297814E-12</v>
       </c>
       <c r="D2">
-        <v>9.052349391846472E-12</v>
+        <v>1.3365466831696E-11</v>
       </c>
       <c r="E2">
-        <v>1.330096733381639E-11</v>
+        <v>1.963837989073328E-11</v>
       </c>
       <c r="F2">
-        <v>1.954355663937905E-11</v>
+        <v>2.885531256868737E-11</v>
       </c>
       <c r="G2">
-        <v>2.871585677955047E-11</v>
+        <v>4.239787056324238E-11</v>
       </c>
       <c r="H2">
-        <v>1.740399552893616E-10</v>
+        <v>2.569636697299418E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5.726043899270747E-08</v>
+        <v>9.313795098585974E-08</v>
       </c>
       <c r="C3">
-        <v>1.095861542080474E-07</v>
+        <v>1.968171596607486E-07</v>
       </c>
       <c r="D3">
-        <v>1.152858155007105E-07</v>
+        <v>1.970501859544101E-07</v>
       </c>
       <c r="E3">
-        <v>1.650904950421461E-07</v>
+        <v>2.478100483777133E-07</v>
       </c>
       <c r="F3">
-        <v>6.15738172430214E-07</v>
+        <v>1.250025780882605E-06</v>
       </c>
       <c r="G3">
-        <v>0.0340549035336651</v>
+        <v>0.0368082585984292</v>
       </c>
       <c r="H3">
-        <v>0.145510718943388</v>
+        <v>0.1280725325827536</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,22 +562,22 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0050345857310621</v>
+        <v>0.0050481185059633</v>
       </c>
       <c r="D4">
-        <v>0.0050345857381473</v>
+        <v>0.00504811851792</v>
       </c>
       <c r="E4">
-        <v>0.0050345857470657</v>
+        <v>0.0050481185334661</v>
       </c>
       <c r="F4">
-        <v>0.0050345857847492</v>
+        <v>0.005048118607973</v>
       </c>
       <c r="G4">
-        <v>0.0050613245617393</v>
+        <v>0.0051099348525145</v>
       </c>
       <c r="H4">
-        <v>0.0052390194929356</v>
+        <v>0.0052857719706471</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,22 +692,22 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>4.130683648511944E-08</v>
+        <v>6.475755026614397E-08</v>
       </c>
       <c r="D9">
-        <v>4.131322012139965E-08</v>
+        <v>6.476601823193796E-08</v>
       </c>
       <c r="E9">
-        <v>4.131955179159323E-08</v>
+        <v>6.477461150112927E-08</v>
       </c>
       <c r="F9">
-        <v>4.132558741842626E-08</v>
+        <v>6.478291914740671E-08</v>
       </c>
       <c r="G9">
-        <v>4.13367654683609E-08</v>
+        <v>6.479860050383117E-08</v>
       </c>
       <c r="H9">
-        <v>1.331305520970348E-07</v>
+        <v>1.994008732321219E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.5155160760053396</v>
+        <v>0.5155160760056104</v>
       </c>
       <c r="C13">
-        <v>0.5155160760070725</v>
+        <v>0.5155160760081563</v>
       </c>
       <c r="D13">
-        <v>0.5155160760106452</v>
+        <v>0.5155160760131775</v>
       </c>
       <c r="E13">
-        <v>0.5155160760199164</v>
+        <v>0.5155160760242662</v>
       </c>
       <c r="F13">
-        <v>0.5155160760348806</v>
+        <v>0.5155160760423756</v>
       </c>
       <c r="G13">
-        <v>0.5155160760646026</v>
+        <v>0.5155160760801575</v>
       </c>
       <c r="H13">
-        <v>0.515516076367971</v>
+        <v>0.5155160764417669</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -923,25 +923,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>7.868835838033028E-08</v>
+        <v>1.426033238479425E-07</v>
       </c>
       <c r="C18">
-        <v>7.871796590056524E-08</v>
+        <v>1.42644413836012E-07</v>
       </c>
       <c r="D18">
-        <v>8.018528064882509E-08</v>
+        <v>1.427660230640154E-07</v>
       </c>
       <c r="E18">
-        <v>1.331465643901503E-07</v>
+        <v>2.114581837581586E-07</v>
       </c>
       <c r="F18">
-        <v>3.388301138560402E-07</v>
+        <v>6.640822978758547E-07</v>
       </c>
       <c r="G18">
-        <v>5.699138530221561E-07</v>
+        <v>1.001181400815497E-06</v>
       </c>
       <c r="H18">
-        <v>4.623363696092672E-06</v>
+        <v>7.769893051102527E-06</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1027,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>3.133660398781358E-08</v>
+        <v>4.647882992946888E-08</v>
       </c>
       <c r="C22">
-        <v>3.135462694953326E-08</v>
+        <v>4.650553346364275E-08</v>
       </c>
       <c r="D22">
-        <v>3.146177211663531E-08</v>
+        <v>4.665466921434541E-08</v>
       </c>
       <c r="E22">
-        <v>4.064583631889292E-08</v>
+        <v>6.043878409411129E-08</v>
       </c>
       <c r="F22">
-        <v>5.688023843387751E-08</v>
+        <v>8.425158233496002E-08</v>
       </c>
       <c r="G22">
-        <v>8.177125109015405E-08</v>
+        <v>1.213735946263894E-07</v>
       </c>
       <c r="H22">
-        <v>5.199998000095061E-07</v>
+        <v>7.709512486889147E-07</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>5.126819446860485E-09</v>
+        <v>7.517047103689221E-09</v>
       </c>
       <c r="D24">
-        <v>1.49314440145806E-08</v>
+        <v>2.16516210077973E-08</v>
       </c>
       <c r="E24">
-        <v>3.70000767588433E-08</v>
+        <v>5.1252996101546E-08</v>
       </c>
       <c r="F24">
-        <v>1.107975323850675E-07</v>
+        <v>1.43943390972018E-07</v>
       </c>
       <c r="G24">
-        <v>3.013363649597253E-07</v>
+        <v>3.539097232131705E-07</v>
       </c>
       <c r="H24">
-        <v>6.561689937077862E-06</v>
+        <v>5.789637011184494E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1160,22 +1160,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>1.210616133560372E-08</v>
+        <v>1.552209524818698E-08</v>
       </c>
       <c r="D27">
-        <v>6.520715501765255E-08</v>
+        <v>8.767531602675866E-08</v>
       </c>
       <c r="E27">
-        <v>0.0181390811844963</v>
+        <v>0.008980152124816799</v>
       </c>
       <c r="F27">
-        <v>0.0329236326446912</v>
+        <v>0.025970470117003</v>
       </c>
       <c r="G27">
-        <v>0.0626550846880302</v>
+        <v>0.052238953226993</v>
       </c>
       <c r="H27">
-        <v>0.1609534127288463</v>
+        <v>0.1296385120317367</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1212,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>2.550044410674565E-08</v>
+        <v>4.273278580189905E-08</v>
       </c>
       <c r="D29">
-        <v>0.07989901757752529</v>
+        <v>0.1111674770014363</v>
       </c>
       <c r="E29">
-        <v>0.1657403319360461</v>
+        <v>0.1706492807612131</v>
       </c>
       <c r="F29">
-        <v>0.2109817251250382</v>
+        <v>0.2236148126329385</v>
       </c>
       <c r="G29">
-        <v>0.2251298597244363</v>
+        <v>0.2251298596333347</v>
       </c>
       <c r="H29">
-        <v>0.2251298598852658</v>
+        <v>0.2251298598476289</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1316,22 +1316,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>2.308523182348088E-08</v>
+        <v>3.204693770715801E-08</v>
       </c>
       <c r="D33">
-        <v>2.782038233121285E-08</v>
+        <v>3.995076166641944E-08</v>
       </c>
       <c r="E33">
-        <v>6.69902103643271E-08</v>
+        <v>8.781313838588938E-08</v>
       </c>
       <c r="F33">
-        <v>1.329116569533236E-07</v>
+        <v>1.70903398082345E-07</v>
       </c>
       <c r="G33">
-        <v>1.420307642703822E-07</v>
+        <v>1.89835591911935E-07</v>
       </c>
       <c r="H33">
-        <v>6.977547924079828E-07</v>
+        <v>9.849887878562516E-07</v>
       </c>
     </row>
     <row r="34" spans="1:8">
